--- a/data/trans_orig/P6704-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6704-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30811</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57151</t>
+          <t>56920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54684</t>
+          <t>54480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87543</t>
+          <t>84588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>42314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71412</t>
+          <t>71373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27458</t>
+          <t>27171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50116</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77449</t>
+          <t>73929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113649</t>
+          <t>111080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>78820</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113031</t>
+          <t>112907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48337</t>
+          <t>47200</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75617</t>
+          <t>75145</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>137252</t>
+          <t>137941</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>180964</t>
+          <t>181395</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>41456</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70669</t>
+          <t>69496</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26979</t>
+          <t>27579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51293</t>
+          <t>50534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74572</t>
+          <t>75049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112076</t>
+          <t>112012</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41262</t>
+          <t>40477</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68202</t>
+          <t>67265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20310</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>40109</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63003</t>
+          <t>67184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98719</t>
+          <t>101237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24633</t>
+          <t>24766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48651</t>
+          <t>48671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>35673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60706</t>
+          <t>61018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66496</t>
+          <t>66056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102326</t>
+          <t>101583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31881</t>
+          <t>33995</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61450</t>
+          <t>61409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36193</t>
+          <t>37253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55610</t>
+          <t>55457</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91006</t>
+          <t>88807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69960</t>
+          <t>67897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101222</t>
+          <t>99248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64047</t>
+          <t>62745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115941</t>
+          <t>117482</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156734</t>
+          <t>156388</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>34783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59902</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32190</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52476</t>
+          <t>53358</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84735</t>
+          <t>85912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32313</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>58439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30371</t>
+          <t>31789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47785</t>
+          <t>48717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80862</t>
+          <t>80533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>35667</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>61288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32940</t>
+          <t>30995</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>55886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84953</t>
+          <t>85951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41362</t>
+          <t>42438</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67663</t>
+          <t>68117</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58653</t>
+          <t>57899</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>88434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78129</t>
+          <t>75962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109004</t>
+          <t>106628</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>24288</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>44547</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108083</t>
+          <t>108158</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>147399</t>
+          <t>145003</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,25%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29739</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55626</t>
+          <t>54235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>24399</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44559</t>
+          <t>42671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72821</t>
+          <t>70993</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33938</t>
+          <t>35303</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58388</t>
+          <t>61486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28687</t>
+          <t>28090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52190</t>
+          <t>50656</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80442</t>
+          <t>82359</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85546</t>
+          <t>87026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123349</t>
+          <t>124472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58561</t>
+          <t>59301</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88356</t>
+          <t>90083</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156709</t>
+          <t>154548</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>201147</t>
+          <t>202830</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56342</t>
+          <t>56451</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>89718</t>
+          <t>88664</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>36428</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62132</t>
+          <t>62423</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101583</t>
+          <t>100981</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>142033</t>
+          <t>141820</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>109773</t>
+          <t>108621</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>148186</t>
+          <t>148510</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>72082</t>
+          <t>72550</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>104681</t>
+          <t>103433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>190389</t>
+          <t>192362</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>239933</t>
+          <t>244077</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49933</t>
+          <t>48095</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78642</t>
+          <t>77769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60577</t>
+          <t>61361</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91192</t>
+          <t>90998</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>132307</t>
+          <t>128107</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43630</t>
+          <t>43526</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72391</t>
+          <t>73526</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32919</t>
+          <t>32271</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58503</t>
+          <t>57897</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>83413</t>
+          <t>83848</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>121933</t>
+          <t>123150</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26385</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46259</t>
+          <t>48032</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38700</t>
+          <t>38985</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64072</t>
+          <t>66141</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>70965</t>
+          <t>71193</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102756</t>
+          <t>103040</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20843</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39943</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45492</t>
+          <t>45805</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49900</t>
+          <t>50094</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79404</t>
+          <t>78478</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>29323</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51694</t>
+          <t>51441</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29965</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52029</t>
+          <t>52577</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>64205</t>
+          <t>64635</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>95503</t>
+          <t>96259</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34730</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40287</t>
+          <t>39974</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>67829</t>
+          <t>68171</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14948</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>32777</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13281</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32825</t>
+          <t>32416</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>57740</t>
+          <t>58374</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>236036</t>
+          <t>232434</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>293962</t>
+          <t>294235</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>196643</t>
+          <t>197827</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>249781</t>
+          <t>250276</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>445592</t>
+          <t>446656</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>526806</t>
+          <t>528609</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>230590</t>
+          <t>228101</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>289447</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>140304</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>189136</t>
+          <t>187511</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>384908</t>
+          <t>382883</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>462701</t>
+          <t>462727</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>405344</t>
+          <t>407092</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>478961</t>
+          <t>480633</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>245619</t>
+          <t>245954</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>301798</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>666891</t>
+          <t>670043</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>763008</t>
+          <t>758840</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>201926</t>
+          <t>200020</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>259664</t>
+          <t>256298</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>128809</t>
+          <t>130429</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>175371</t>
+          <t>175753</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>343976</t>
+          <t>343344</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>415858</t>
+          <t>417368</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>194708</t>
+          <t>194103</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>253580</t>
+          <t>253727</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>111563</t>
+          <t>110890</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>154979</t>
+          <t>156724</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>318245</t>
+          <t>323010</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>395965</t>
+          <t>397127</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>35363</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61161</t>
+          <t>62012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38096</t>
+          <t>36721</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62987</t>
+          <t>61694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82003</t>
+          <t>80207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117102</t>
+          <t>114940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40417</t>
+          <t>39216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66446</t>
+          <t>67481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>27126</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49086</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73050</t>
+          <t>73384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108383</t>
+          <t>110841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64894</t>
+          <t>63951</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96210</t>
+          <t>95423</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52357</t>
+          <t>52129</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79280</t>
+          <t>79780</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>124519</t>
+          <t>122871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>166997</t>
+          <t>165404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>38667</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65902</t>
+          <t>65672</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>25731</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47383</t>
+          <t>48532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70755</t>
+          <t>72916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105902</t>
+          <t>105600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>35546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63280</t>
+          <t>61567</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37607</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58401</t>
+          <t>58317</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89853</t>
+          <t>91014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75445</t>
+          <t>75207</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>31113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54770</t>
+          <t>54771</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85991</t>
+          <t>86718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122010</t>
+          <t>123563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31455</t>
+          <t>32774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>58360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33442</t>
+          <t>32377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56820</t>
+          <t>54983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70420</t>
+          <t>70312</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105018</t>
+          <t>105952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54254</t>
+          <t>53754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82528</t>
+          <t>83372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49138</t>
+          <t>49484</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74417</t>
+          <t>75046</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109960</t>
+          <t>111512</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149009</t>
+          <t>150161</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32544</t>
+          <t>31820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57769</t>
+          <t>58201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33815</t>
+          <t>33117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53937</t>
+          <t>53245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85313</t>
+          <t>85620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29375</t>
+          <t>28033</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59617</t>
+          <t>60990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30420</t>
+          <t>30749</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54437</t>
+          <t>54710</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26819</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47189</t>
+          <t>48967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74390</t>
+          <t>75269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24348</t>
+          <t>24902</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45241</t>
+          <t>46441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>21162</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37645</t>
+          <t>36334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63348</t>
+          <t>62063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58775</t>
+          <t>59571</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86731</t>
+          <t>87212</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21682</t>
+          <t>21681</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70944</t>
+          <t>69874</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103852</t>
+          <t>102746</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33289</t>
+          <t>31486</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57564</t>
+          <t>56809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22088</t>
+          <t>22879</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47658</t>
+          <t>45625</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75417</t>
+          <t>73157</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>15893</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34344</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43018</t>
+          <t>42758</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97500</t>
+          <t>97084</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135251</t>
+          <t>136746</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68142</t>
+          <t>67476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99437</t>
+          <t>99675</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>173912</t>
+          <t>174546</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223116</t>
+          <t>224971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61198</t>
+          <t>61012</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93100</t>
+          <t>94252</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54602</t>
+          <t>54299</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83368</t>
+          <t>83722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>123161</t>
+          <t>122709</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>166356</t>
+          <t>168446</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>138694</t>
+          <t>138081</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>181244</t>
+          <t>179104</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>82462</t>
+          <t>84744</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>117313</t>
+          <t>118906</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>233872</t>
+          <t>230470</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>288018</t>
+          <t>287818</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>76815</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110019</t>
+          <t>110583</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60926</t>
+          <t>60488</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92944</t>
+          <t>93666</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>145966</t>
+          <t>144015</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>193837</t>
+          <t>191414</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32947</t>
+          <t>32885</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59791</t>
+          <t>60064</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>29329</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55598</t>
+          <t>54975</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>69276</t>
+          <t>71216</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>105009</t>
+          <t>105186</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51886</t>
+          <t>51956</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>79878</t>
+          <t>78660</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>54982</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>82639</t>
+          <t>81933</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>114601</t>
+          <t>115748</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>153406</t>
+          <t>154282</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26861</t>
+          <t>27135</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50108</t>
+          <t>50144</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23140</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45043</t>
+          <t>44131</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>55734</t>
+          <t>55925</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85581</t>
+          <t>88109</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36335</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>60282</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>47227</t>
+          <t>45997</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72663</t>
+          <t>71464</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>88056</t>
+          <t>90474</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>126530</t>
+          <t>126201</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36560</t>
+          <t>36540</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>40857</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>43074</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>70624</t>
+          <t>71348</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26812</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>34900</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>297852</t>
+          <t>296085</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>364025</t>
+          <t>361946</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>234798</t>
+          <t>233223</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>290331</t>
+          <t>291684</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>547898</t>
+          <t>549192</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>636841</t>
+          <t>631038</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>213395</t>
+          <t>211755</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>272993</t>
+          <t>273307</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>171670</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>221121</t>
+          <t>221581</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>402543</t>
+          <t>399510</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>485790</t>
+          <t>476049</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>391655</t>
+          <t>392772</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>461577</t>
+          <t>463506</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>271036</t>
+          <t>269058</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>330883</t>
+          <t>331015</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>685932</t>
+          <t>683547</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>778999</t>
+          <t>774760</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>230783</t>
+          <t>232805</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>290176</t>
+          <t>293943</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>158244</t>
+          <t>155149</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>206958</t>
+          <t>206353</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>404991</t>
+          <t>400244</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>481205</t>
+          <t>478297</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>138043</t>
+          <t>135475</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>185178</t>
+          <t>186432</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>80658</t>
+          <t>80892</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>116513</t>
+          <t>118749</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>228134</t>
+          <t>228042</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>292065</t>
+          <t>293319</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -9377,32 +9377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28905</t>
+          <t>30290</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19024</t>
+          <t>21130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37975</t>
+          <t>43489</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9412,32 +9412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23586</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>18784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31468</t>
+          <t>33748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9447,32 +9447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52491</t>
+          <t>55856</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40176</t>
+          <t>42754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65612</t>
+          <t>69696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -9490,32 +9490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27475</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9525,32 +9525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20823</t>
+          <t>22232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32121</t>
+          <t>35103</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42703</t>
+          <t>46787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -9603,32 +9603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19222</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>34407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9638,32 +9638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>21895</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>29771</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9673,32 +9673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>39763</t>
+          <t>45940</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52002</t>
+          <t>58231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -9716,32 +9716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18563</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9751,32 +9751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18378</t>
+          <t>19757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9786,32 +9786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23585</t>
+          <t>25378</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33316</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -9829,32 +9829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>24770</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9864,32 +9864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9899,32 +9899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36168</t>
+          <t>37724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -9942,17 +9942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9977,17 +9977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80978</t>
+          <t>86015</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80978</t>
+          <t>86015</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80978</t>
+          <t>86015</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>169976</t>
+          <t>186022</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>169976</t>
+          <t>186022</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>169976</t>
+          <t>186022</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10059,32 +10059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23877</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>35193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10094,32 +10094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>20678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31278</t>
+          <t>35925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10129,32 +10129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48719</t>
+          <t>54360</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39263</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59683</t>
+          <t>65424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -10172,32 +10172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10207,32 +10207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10242,32 +10242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>26528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -10285,32 +10285,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10320,32 +10320,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10355,32 +10355,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40945</t>
+          <t>40933</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30935</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52213</t>
+          <t>52948</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -10398,32 +10398,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13573</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10433,32 +10433,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10468,32 +10468,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18211</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -10511,32 +10511,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10546,32 +10546,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10581,32 +10581,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>16142</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>25714</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -10624,17 +10624,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10659,17 +10659,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10741,32 +10741,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>263403</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76920</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>300641</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10776,32 +10776,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10811,32 +10811,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>268930</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81984</t>
+          <t>18383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>321342</t>
+          <t>39874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -10854,32 +10854,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>24323</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10924,32 +10924,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65074</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -10967,32 +10967,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>13665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75131</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11002,32 +11002,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>26900</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>19060</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103735</t>
+          <t>38318</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -11080,32 +11080,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59126</t>
+          <t>22068</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11115,32 +11115,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60776</t>
+          <t>27642</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -11193,32 +11193,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46356</t>
+          <t>17852</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>9613</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11263,32 +11263,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51509</t>
+          <t>22612</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -11306,17 +11306,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11341,17 +11341,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11376,17 +11376,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11423,17 +11423,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>49977</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33861</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57905</t>
+          <t>63538</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11443,12 +11443,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11458,32 +11458,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31089</t>
+          <t>34014</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>42446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11493,32 +11493,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>77089</t>
+          <t>83991</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63432</t>
+          <t>69306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92383</t>
+          <t>100945</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -11536,32 +11536,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11571,32 +11571,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26759</t>
+          <t>29771</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11606,32 +11606,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>30915</t>
+          <t>34707</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>24975</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41593</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -11649,32 +11649,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38823</t>
+          <t>40079</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>28696</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51514</t>
+          <t>51564</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11684,32 +11684,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>29859</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22613</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38462</t>
+          <t>41726</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11719,32 +11719,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>68682</t>
+          <t>73208</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>54989</t>
+          <t>58787</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83388</t>
+          <t>87348</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -11762,32 +11762,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11797,32 +11797,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>27247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11832,32 +11832,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>37454</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>26721</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45190</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -11875,32 +11875,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>23559</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11910,32 +11910,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11945,32 +11945,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31163</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12023,17 +12023,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>105404</t>
+          <t>117375</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>105404</t>
+          <t>117375</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>105404</t>
+          <t>117375</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12058,17 +12058,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>229145</t>
+          <t>251837</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>229145</t>
+          <t>251837</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>229145</t>
+          <t>251837</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12105,32 +12105,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>40641</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20472</t>
+          <t>27871</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42214</t>
+          <t>54079</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12140,32 +12140,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>31849</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20905</t>
+          <t>23427</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34858</t>
+          <t>39984</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12175,22 +12175,22 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>58978</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46081</t>
+          <t>56966</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73756</t>
+          <t>87499</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>48,44%</t>
         </is>
       </c>
     </row>
@@ -12218,32 +12218,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18359</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12253,32 +12253,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20508</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12288,32 +12288,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>23082</t>
+          <t>25690</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>16736</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34153</t>
+          <t>36517</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -12331,32 +12331,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>22389</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26705</t>
+          <t>32714</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12366,22 +12366,22 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12401,32 +12401,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>44713</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>33657</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45451</t>
+          <t>56877</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -12444,32 +12444,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>13757</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21533</t>
+          <t>27923</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12479,32 +12479,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12514,32 +12514,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>24970</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>29404</t>
+          <t>40230</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -12557,32 +12557,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14370</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12592,32 +12592,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12627,32 +12627,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -12670,17 +12670,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>72216</t>
+          <t>92395</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>72216</t>
+          <t>92395</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72216</t>
+          <t>92395</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12705,17 +12705,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12740,17 +12740,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>146102</t>
+          <t>180630</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>146102</t>
+          <t>180630</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>146102</t>
+          <t>180630</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12787,32 +12787,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>393392</t>
+          <t>169604</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>224280</t>
+          <t>147358</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>552469</t>
+          <t>196862</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12822,32 +12822,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>112815</t>
+          <t>125670</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>98089</t>
+          <t>109236</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>129800</t>
+          <t>144315</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12857,32 +12857,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>506207</t>
+          <t>295274</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>334096</t>
+          <t>267151</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>778269</t>
+          <t>327633</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -12900,32 +12900,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>60920</t>
+          <t>66093</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>51375</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>103320</t>
+          <t>83819</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12935,32 +12935,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>56646</t>
+          <t>63558</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>46733</t>
+          <t>51953</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>68706</t>
+          <t>77732</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12970,32 +12970,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>117565</t>
+          <t>129651</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>49282</t>
+          <t>109836</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>164175</t>
+          <t>153494</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -13013,32 +13013,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>128007</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>41713</t>
+          <t>106295</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>192392</t>
+          <t>150890</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>93325</t>
+          <t>103687</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>79263</t>
+          <t>89019</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>108840</t>
+          <t>120283</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13083,32 +13083,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>209417</t>
+          <t>231694</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>102680</t>
+          <t>204730</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>287003</t>
+          <t>258575</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -13126,32 +13126,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>63044</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17786</t>
+          <t>46047</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>92399</t>
+          <t>82974</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13161,32 +13161,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>46441</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>40061</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>57094</t>
+          <t>64704</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13196,32 +13196,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>99027</t>
+          <t>114876</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>39154</t>
+          <t>95436</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>138055</t>
+          <t>137883</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -13239,32 +13239,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>41175</t>
+          <t>45251</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>73427</t>
+          <t>62433</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13274,32 +13274,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>43079</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>28498</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>50073</t>
+          <t>54998</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13309,32 +13309,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>79855</t>
+          <t>88330</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>69675</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>112702</t>
+          <t>109668</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>664164</t>
+          <t>471999</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>664164</t>
+          <t>471999</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>664164</t>
+          <t>471999</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13387,17 +13387,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>347907</t>
+          <t>387826</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>347907</t>
+          <t>387826</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>347907</t>
+          <t>387826</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13422,17 +13422,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1012071</t>
+          <t>859825</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1012071</t>
+          <t>859825</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1012071</t>
+          <t>859825</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
